--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486889_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486889_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.077</v>
+        <v>6.3597</v>
       </c>
       <c r="E2" t="n">
-        <v>8.946899999999999</v>
+        <v>7.3779</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8699</v>
+        <v>-1.0181</v>
       </c>
       <c r="G2" t="n">
         <v>0.1617</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2562</v>
+        <v>1.539</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9984</v>
+        <v>1.4294</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2578</v>
+        <v>0.1096</v>
       </c>
       <c r="V2" t="n">
         <v>3.0164</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7372</v>
+        <v>1.8425</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7797</v>
+        <v>3.8257</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0425</v>
+        <v>-1.9833</v>
       </c>
       <c r="G3" t="n">
         <v>0.6433</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2162</v>
+        <v>0.8891</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4225</v>
+        <v>0.6236</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2062</v>
+        <v>0.2655</v>
       </c>
       <c r="V3" t="n">
         <v>0.3101</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3542</v>
+        <v>0.125</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7097</v>
+        <v>4.5556</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3555</v>
+        <v>-4.4306</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3888</v>
+        <v>-2.4008</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4052</v>
+        <v>-0.6325</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9836</v>
+        <v>-1.7683</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0129</v>
+        <v>3.3552</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1844</v>
+        <v>-0.0516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1973</v>
+        <v>3.4067</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4017</v>
+        <v>-5.756</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2208</v>
+        <v>-0.581</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.181</v>
+        <v>-5.175</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>2.6694</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7779</v>
+        <v>1.0741</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6968</v>
+        <v>1.3093</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.2352</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3491</v>
+        <v>-1.2177</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3491</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4291</v>
+        <v>-0.4884</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2246</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2045</v>
+        <v>-0.2638</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3818</v>
@@ -844,13 +844,13 @@
         <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2526</v>
+        <v>-0.3119</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0109</v>
+        <v>-0.0484</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9175</v>
+        <v>-0.5897</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6459</v>
+        <v>-0.4367</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2716</v>
+        <v>-0.153</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2061</v>
@@ -922,13 +922,13 @@
         <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2658</v>
+        <v>0.062</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0659</v>
+        <v>0.1433</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V6" t="n">
         <v>0.3491</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9193</v>
+        <v>-0.7215</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7188</v>
+        <v>0.6637</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6381</v>
+        <v>-1.3852</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4008</v>
+        <v>-2.3888</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6325</v>
+        <v>-0.4052</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7683</v>
+        <v>-1.9836</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3552</v>
+        <v>0.0129</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0516</v>
+        <v>-0.1844</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4067</v>
+        <v>0.1973</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.756</v>
+        <v>-2.4017</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.581</v>
+        <v>-0.2208</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.175</v>
+        <v>-2.181</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0298</v>
+        <v>0.7022</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4725</v>
+        <v>0.6508</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4427</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2177</v>
+        <v>0.3491</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1088</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1734</v>
+        <v>-1.7486</v>
       </c>
       <c r="E8" t="n">
-        <v>1.089</v>
+        <v>-0.9389</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2624</v>
+        <v>-0.8097</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3918</v>
+        <v>-2.7444</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2418</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.6335</v>
+        <v>-2.1733</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1702</v>
+        <v>-1.0822</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1836</v>
+        <v>0.2336</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0134</v>
+        <v>-1.3158</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5619</v>
+        <v>-1.6623</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0582</v>
+        <v>-0.8047</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6201</v>
+        <v>-0.8575</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2321</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>2.629</v>
+        <v>-0.5463</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9989</v>
+        <v>-0.097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6301</v>
+        <v>-0.4493</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>0.3101</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9717</v>
+        <v>-2.1288</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3656</v>
+        <v>0.2522</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6061</v>
+        <v>-2.381</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.3502</v>
+        <v>-1.3918</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5428</v>
+        <v>2.2418</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8074</v>
+        <v>-3.6335</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0748</v>
+        <v>2.1702</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3772</v>
+        <v>2.1836</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3024</v>
+        <v>-0.0134</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2753</v>
+        <v>-3.5619</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1656</v>
+        <v>0.0582</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.1098</v>
+        <v>-3.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5571</v>
+        <v>1.6736</v>
       </c>
       <c r="T9" t="n">
-        <v>0.736</v>
+        <v>1.1621</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.5115</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2577</v>
+        <v>-2.4651</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5665</v>
+        <v>1.3266</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6911</v>
+        <v>-3.7917</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7444</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5711000000000001</v>
+        <v>3.0529</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1733</v>
+        <v>-3.8891</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0822</v>
+        <v>2.0706</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2336</v>
+        <v>3.663</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3158</v>
+        <v>-1.5924</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6623</v>
+        <v>-2.9068</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8047</v>
+        <v>-0.6101</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8575</v>
+        <v>-2.2967</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0553</v>
+        <v>-0.093</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7246</v>
+        <v>0.2827</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3307</v>
+        <v>-0.3757</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3101</v>
+        <v>-2.3573</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0698</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8669</v>
+        <v>-2.5844</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8444</v>
+        <v>-0.7398</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0225</v>
+        <v>-1.8446</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0935</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1649</v>
+        <v>0.4474</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2749</v>
+        <v>0.3795</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.11</v>
+        <v>0.0679</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1704</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6436</v>
+        <v>-2.6116</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3852</v>
+        <v>-1.6794</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0288</v>
+        <v>-0.9322</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-4.3502</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0529</v>
+        <v>-2.5428</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8891</v>
+        <v>-1.8074</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0706</v>
+        <v>-1.0748</v>
       </c>
       <c r="K12" t="n">
-        <v>3.663</v>
+        <v>-2.3772</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5924</v>
+        <v>1.3024</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9068</v>
+        <v>-3.2753</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6101</v>
+        <v>-0.1656</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2967</v>
+        <v>-3.1098</v>
       </c>
       <c r="P12" t="n">
         <v>0.8214</v>
@@ -1390,22 +1390,22 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2716</v>
+        <v>0.9172</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6587</v>
+        <v>0.4222</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6129</v>
+        <v>0.4951</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0108</v>
+        <v>-5.0109</v>
       </c>
       <c r="E13" t="n">
         <v>13.9823</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.993</v>
+        <v>-18.9932</v>
       </c>
       <c r="G13" t="n">
         <v>-18.9886</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3883</v>
+        <v>5.388299999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-24.3767</v>
@@ -1444,7 +1444,7 @@
         <v>12.355</v>
       </c>
       <c r="K13" t="n">
-        <v>9.120899999999999</v>
+        <v>9.120900000000001</v>
       </c>
       <c r="L13" t="n">
         <v>3.234</v>
@@ -1471,13 +1471,13 @@
         <v>6.3534</v>
       </c>
       <c r="T13" t="n">
-        <v>6.0423</v>
+        <v>6.042400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3110000000000001</v>
+        <v>0.3111</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5892000000000004</v>
+        <v>-0.5892000000000005</v>
       </c>
       <c r="W13" t="n">
         <v>3.7987</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0071</v>
+        <v>7.2739</v>
       </c>
       <c r="E14" t="n">
         <v>9.083600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0764</v>
+        <v>-1.8097</v>
       </c>
       <c r="G14" t="n">
         <v>8.131500000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7753</v>
+        <v>-0.5085</v>
       </c>
       <c r="T14" t="n">
         <v>0.2517</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.027</v>
+        <v>-0.7602</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3491</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5914</v>
+        <v>5.8006</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4632</v>
+        <v>5.6724</v>
       </c>
       <c r="F15" t="n">
         <v>0.1282</v>
@@ -1624,10 +1624,10 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3952</v>
+        <v>0.6044</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0155</v>
+        <v>0.2247</v>
       </c>
       <c r="U15" t="n">
         <v>0.3798</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6315</v>
+        <v>2.0482</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5281</v>
+        <v>2.7373</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8966</v>
+        <v>-0.6891</v>
       </c>
       <c r="G16" t="n">
         <v>3.476</v>
@@ -1702,13 +1702,13 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7911</v>
+        <v>-1.3744</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7246</v>
+        <v>-0.5154</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0665</v>
+        <v>-0.859</v>
       </c>
       <c r="V16" t="n">
         <v>1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4996</v>
+        <v>1.0663</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7183</v>
+        <v>4.1367</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2186</v>
+        <v>-3.0704</v>
       </c>
       <c r="G17" t="n">
         <v>6.0371</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.6093</v>
+        <v>-2.0427</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7169</v>
+        <v>-0.2985</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8924</v>
+        <v>-1.7442</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0857</v>
+        <v>-0.357</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6739</v>
+        <v>0.8988</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7597</v>
+        <v>-1.2558</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7732</v>
+        <v>-0.0519</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4441</v>
+        <v>-1.9857</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3291</v>
+        <v>1.9338</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0348</v>
+        <v>0.7284</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5217</v>
+        <v>-0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5131</v>
+        <v>1.3284</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2616</v>
+        <v>-0.7803</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0777</v>
+        <v>-1.3857</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1839</v>
+        <v>0.6054</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5599</v>
+        <v>-0.8862</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0149</v>
+        <v>0.1704</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.455</v>
+        <v>-1.0566</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0698</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4459</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8988</v>
+        <v>0.9417</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3447</v>
+        <v>-1.9079</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0519</v>
+        <v>0.7732</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9857</v>
+        <v>0.4441</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9338</v>
+        <v>0.3291</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7284</v>
+        <v>2.0348</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6</v>
+        <v>1.5217</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3284</v>
+        <v>0.5131</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7803</v>
+        <v>-1.2616</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3857</v>
+        <v>-1.0777</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6054</v>
+        <v>-0.1839</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9752</v>
+        <v>-0.3205</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1704</v>
+        <v>0.2827</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1455</v>
+        <v>-0.6032</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-1.1768</v>
       </c>
       <c r="E20" t="n">
         <v>1.0926</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9137</v>
+        <v>-2.2694</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5648</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4966</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1435</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.353</v>
+        <v>-0.7087</v>
       </c>
       <c r="V20" t="n">
         <v>0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2038</v>
+        <v>-1.5909</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.198</v>
+        <v>-1.4072</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0058</v>
+        <v>-0.1837</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7594</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9663</v>
+        <v>0.5792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3757</v>
+        <v>0.1665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5906</v>
+        <v>0.4127</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8837</v>
+        <v>-2.5532</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1599</v>
+        <v>-1.4737</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7238</v>
+        <v>-1.0795</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7741</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6851</v>
+        <v>0.0156</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3021</v>
+        <v>-0.0117</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3829</v>
+        <v>0.0272</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2787</v>
+        <v>-4.5342</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1075</v>
+        <v>-2.6891</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1712</v>
+        <v>-1.8451</v>
       </c>
       <c r="G23" t="n">
         <v>-2.235</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3126</v>
+        <v>-1.5681</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8563</v>
+        <v>-0.4379</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4563</v>
+        <v>-1.1302</v>
       </c>
       <c r="V23" t="n">
         <v>1.5277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.010700000000003</v>
+        <v>5.0107</v>
       </c>
       <c r="E24" t="n">
         <v>18.9931</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.9823</v>
+        <v>-13.9824</v>
       </c>
       <c r="G24" t="n">
         <v>18.9885</v>
@@ -2326,13 +2326,13 @@
         <v>8.213700000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.3536</v>
+        <v>-6.3535</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3110000000000003</v>
+        <v>-0.3109999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.042399999999999</v>
+        <v>-6.042400000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.5892000000000002</v>
